--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_maule.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:29</t>
+    <t xml:space="preserve">2026-09-09 20:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2019_maule.xlsx
@@ -24,90 +24,90 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Maule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:29</t>
+    <t xml:space="preserve">2026-09-18 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.63</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.05</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.83</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="8">
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.51</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +591,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
@@ -599,7 +599,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.81</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.64</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.04</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.75</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="14">
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="15">
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="16">
@@ -647,7 +647,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17">
@@ -655,7 +655,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -679,7 +679,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4.46</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="21">
@@ -687,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="22">
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="23">
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.19</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="24">
@@ -711,7 +711,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2.54</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="25">
@@ -719,7 +719,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5.63</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="26">
@@ -727,7 +727,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.62</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="27">
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.24</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="28">
@@ -743,7 +743,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3.14</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +751,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3.62</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="30">
